--- a/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est l'heure du dîner. Tom est dans la cuisine. Papa pose les assiettes. Maman apporte le pain. Tom va s'asseoir. Il pose les fesses sur la chaise. Il est assis à table. Papa s'assoit aussi. Maman s'assoit près de Tom. Ils mangent ensemble. Tom tient sa cuillère. Il mange assis. La chaise est stable. Papa dit : on mange ensemble, à table. Tom sourit. Il reste assis. Maman coupe le pain. Tom attend, assis. Ils sont ensemble à table.</t>
+          <t>C'est l'heure du dîner. Tom est dans la cuisine. Papa pose les assiettes. Maman apporte le pain. Tom va s'asseoir. Il pose les fesses sur la chaise. Il est assis à table. Papa s'assoit aussi. Maman s'assoit près de Tom. Ils mangent ensemble. Tom tient sa cuillère. Il mange assis. La chaise est stable. On mange ensemble, à table. Tom sourit. Il reste assis. Maman coupe le pain. Tom attend, assis. Ils sont ensemble à table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est l'heure du dîner. Tom est dans la cuisine. Papa pose les assiettes. Maman apporte le pain. Tom va s'asseoir. Il pose les fesses sur la chaise. Il est assis à table. Papa s'assoit aussi. Maman s'assoit près de Tom. Ils mangent ensemble. Tom tient sa cuillère. Il mange assis. La chaise est stable.
+papa|On mange ensemble, à table.
+narrateur|Tom sourit. Il reste assis. Maman coupe le pain. Tom attend, assis. Ils sont ensemble à table.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va manger. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom est assis. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Tom boit une gorgée. Il reste assis jusqu'à la fin. Merci, dit maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Tom sourit. Il reste assis. Maman coupe le pain. Tom attend, assis. Ils sont ensemble à table.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Tom va manger. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Tom est assis. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Tom boit une gorgée. Il reste assis jusqu'à la fin. Merci, dit maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tom s'assoit à table</t>
+          <t>Le bateau de Tom</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La soupe fume. La chaise de Tom est son bateau pour rejoindre la table en famille.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est l'heure du dîner. Tom est dans la cuisine. Papa pose les assiettes. Maman apporte le pain. Tom va s'asseoir. Il pose les fesses sur la chaise. Il est assis à table. Papa s'assoit aussi. Maman s'assoit près de Tom. Ils mangent ensemble. Tom tient sa cuillère. Il mange assis. La chaise est stable. On mange ensemble, à table. Tom sourit. Il reste assis. Maman coupe le pain. Tom attend, assis. Ils sont ensemble à table.</t>
+          <t>Tom est dans le couloir. Il sent quelque chose. Ça sent la soupe. Une petite fumée danse dans la cuisine. Tom ! Viens, Tom ! La soupe fume. Elle est prête. Tom arrive. Il voit les assiettes. La soupe fume encore. Sa chaise l'attend, près de la table. C'est mon bateau. Oui. Ton bateau va à table. Tom pousse un peu la chaise. Il pose les fesses sur la chaise. Le bateau glisse tout près. Tom s'assoit. Il est assis. Papa s'assoit aussi. Maman s'assoit près de Tom. Ils sont ensemble, à table. La soupe fume tout près. Mon bateau est arrivé. Oui. On est ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,36 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est l'heure du dîner. Tom est dans la cuisine. Papa pose les assiettes. Maman apporte le pain. Tom va s'asseoir. Il pose les fesses sur la chaise. Il est assis à table. Papa s'assoit aussi. Maman s'assoit près de Tom. Ils mangent ensemble. Tom tient sa cuillère. Il mange assis. La chaise est stable.
-papa|On mange ensemble, à table.
-narrateur|Tom sourit. Il reste assis. Maman coupe le pain. Tom attend, assis. Ils sont ensemble à table.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Tom est dans le couloir.
+narrateur|Il sent quelque chose.
+narrateur|Ça sent la soupe.
+narrateur|Une petite fumée danse dans la cuisine.
+papa|Tom ! Viens, Tom !
+maman|La soupe fume. Elle est prête.
+narrateur|Tom arrive.
+narrateur|Il voit les assiettes.
+narrateur|La soupe fume encore.
+narrateur|Sa chaise l'attend, près de la table.
+enfant-m|C'est mon bateau.
+papa|Oui. Ton bateau va à table.
+narrateur|Tom pousse un peu la chaise.
+narrateur|Il pose les fesses sur la chaise.
+narrateur|Le bateau glisse tout près.
+narrateur|Tom s'assoit.
+narrateur|Il est assis.
+narrateur|Papa s'assoit aussi.
+narrateur|Maman s'assoit près de Tom.
+narrateur|Ils sont ensemble, à table.
+narrateur|La soupe fume tout près.
+enfant-m|Mon bateau est arrivé.
+maman|Oui. On est ensemble.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pas,chaise</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1378,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tom va manger. Que fait-il ?</t>
+          <t>Le bateau de Tom s'arrête. Tom est où ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,10 +1534,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Tom va manger. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Le bateau de Tom s'arrête. Tom est où ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1526,7 +1561,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom est assis. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
+          <t>Tom est assis. Les fesses sont sur la chaise. Papa et maman sont avec lui. Ils sont ensemble, à table.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,10 +1705,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Tom est assis. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Tom est assis.
+narrateur|Les fesses sont sur la chaise.
+narrateur|Papa et maman sont avec lui.
+narrateur|Ils sont ensemble, à table.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>chaise</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1698,7 +1740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tom boit une gorgée. Il reste assis jusqu'à la fin. Merci, dit maman.</t>
+          <t>La soupe n'attend plus. Tom prend sa cuillère. On commence. Tom goûte. C'est chaud. C'est bon. Bon appétit, Tom. Ils mangent ensemble. Tom reste assis, à table. Merci, maman. Merci, papa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,10 +1880,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Tom boit une gorgée. Il reste assis jusqu'à la fin. Merci, dit maman.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La soupe n'attend plus.
+narrateur|Tom prend sa cuillère.
+papa|On commence.
+narrateur|Tom goûte.
+enfant-m|C'est chaud. C'est bon.
+maman|Bon appétit, Tom.
+narrateur|Ils mangent ensemble.
+narrateur|Tom reste assis, à table.
+enfant-m|Merci, maman. Merci, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1866,7 +1915,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La fumée de la soupe s'en va. Le bateau de Tom est resté à table. On a mangé ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,10 +2055,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La fumée de la soupe s'en va.
+enfant-m|Le bateau de Tom est resté à table.
+maman|On a mangé ensemble.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2117,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit captivant, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>La soupe fume. La chaise de Tom est son bateau pour rejoindre la table en famille.</t>
+          <t>La chaise de Tom, c'est son bateau. Le bateau va jusqu'à la table. Tom s'assoit avec papa et maman. On mange.</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom est dans le couloir. Il sent quelque chose. Ça sent la soupe. Une petite fumée danse dans la cuisine. Tom ! Viens, Tom ! La soupe fume. Elle est prête. Tom arrive. Il voit les assiettes. La soupe fume encore. Sa chaise l'attend, près de la table. C'est mon bateau. Oui. Ton bateau va à table. Tom pousse un peu la chaise. Il pose les fesses sur la chaise. Le bateau glisse tout près. Tom s'assoit. Il est assis. Papa s'assoit aussi. Maman s'assoit près de Tom. Ils sont ensemble, à table. La soupe fume tout près. Mon bateau est arrivé. Oui. On est ensemble.</t>
+          <t>Tom est dans le couloir. Il lève le nez. Ça sent la soupe. Une petite fumée danse. Tom ! Viens, Tom ! La soupe est prête. Tom arrive. Il voit sa chaise. La chaise est un peu loin. C'est mon bateau ! Oui. Ta chaise, c'est ton bateau. Tom s'assoit. Il pousse un peu. Le bateau va jusqu'à la table. Papa s'assoit aussi. Maman s'assoit près de Tom.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,28 +1325,23 @@
       <c r="AW2" t="inlineStr">
         <is>
           <t>narrateur|Tom est dans le couloir.
-narrateur|Il sent quelque chose.
+narrateur|Il lève le nez.
 narrateur|Ça sent la soupe.
-narrateur|Une petite fumée danse dans la cuisine.
-papa|Tom ! Viens, Tom !
-maman|La soupe fume. Elle est prête.
+narrateur|Une petite fumée danse.
+papa|Tom !
+papa|Viens, Tom !
+maman|La soupe est prête.
 narrateur|Tom arrive.
-narrateur|Il voit les assiettes.
-narrateur|La soupe fume encore.
-narrateur|Sa chaise l'attend, près de la table.
-enfant-m|C'est mon bateau.
-papa|Oui. Ton bateau va à table.
-narrateur|Tom pousse un peu la chaise.
-narrateur|Il pose les fesses sur la chaise.
-narrateur|Le bateau glisse tout près.
+narrateur|Il voit sa chaise.
+narrateur|La chaise est un peu loin.
+enfant-m|C'est mon bateau !
+papa|Oui.
+papa|Ta chaise, c'est ton bateau.
 narrateur|Tom s'assoit.
-narrateur|Il est assis.
+narrateur|Il pousse un peu.
+narrateur|Le bateau va jusqu'à la table.
 narrateur|Papa s'assoit aussi.
-narrateur|Maman s'assoit près de Tom.
-narrateur|Ils sont ensemble, à table.
-narrateur|La soupe fume tout près.
-enfant-m|Mon bateau est arrivé.
-maman|Oui. On est ensemble.</t>
+narrateur|Maman s'assoit près de Tom.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1378,7 +1373,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le bateau de Tom s'arrête. Tom est où ?</t>
+          <t>Le bateau s'arrête. Tom est où ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1534,9 +1529,11 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le bateau de Tom s'arrête. Tom est où ?</t>
-        </is>
-      </c>
+          <t>narrateur|Le bateau s'arrête.
+narrateur|Tom est où ?</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1561,7 +1558,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom est assis. Les fesses sont sur la chaise. Papa et maman sont avec lui. Ils sont ensemble, à table.</t>
+          <t>Tom est assis. Il est à table. Papa et maman sont avec lui. On est ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1706,16 +1703,12 @@
       <c r="AW4" t="inlineStr">
         <is>
           <t>narrateur|Tom est assis.
-narrateur|Les fesses sont sur la chaise.
+narrateur|Il est à table.
 narrateur|Papa et maman sont avec lui.
-narrateur|Ils sont ensemble, à table.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>chaise</t>
-        </is>
-      </c>
+maman|On est ensemble.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1740,7 +1733,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La soupe n'attend plus. Tom prend sa cuillère. On commence. Tom goûte. C'est chaud. C'est bon. Bon appétit, Tom. Ils mangent ensemble. Tom reste assis, à table. Merci, maman. Merci, papa.</t>
+          <t>La soupe est là. Tom prend sa cuillère. C'est chaud. C'est bon. Bon appétit, Tom. Ils mangent ensemble. Tom reste assis. Merci, maman. Merci, papa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1880,17 +1873,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|La soupe n'attend plus.
+          <t>narrateur|La soupe est là.
 narrateur|Tom prend sa cuillère.
-papa|On commence.
-narrateur|Tom goûte.
-enfant-m|C'est chaud. C'est bon.
+enfant-m|C'est chaud.
+enfant-m|C'est bon.
 maman|Bon appétit, Tom.
 narrateur|Ils mangent ensemble.
-narrateur|Tom reste assis, à table.
-enfant-m|Merci, maman. Merci, papa.</t>
-        </is>
-      </c>
+narrateur|Tom reste assis.
+enfant-m|Merci, maman.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1915,7 +1909,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La fumée de la soupe s'en va. Le bateau de Tom est resté à table. On a mangé ensemble. L'histoire est finie.</t>
+          <t>La fumée s'en va. Le bateau de Tom reste à table. On a mangé assis, ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2055,12 +2049,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|La fumée de la soupe s'en va.
-enfant-m|Le bateau de Tom est resté à table.
-maman|On a mangé ensemble.
+          <t>narrateur|La fumée s'en va.
+narrateur|Le bateau de Tom reste à table.
+maman|On a mangé assis, ensemble.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2079,7 +2074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2122,6 +2117,13 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit captivant, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>F-NAR-008 récit captivant, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -841,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>La chaise de Tom, c'est son bateau. Le bateau va jusqu'à la table. Tom s'assoit avec papa et maman. On mange.</t>
+          <t>La chaise de Tom, c'est son bateau. Le bateau va jusqu'à la table. Tom s'assoit avec papa et maman. Il goûte la soupe. On mange.</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom est dans le couloir. Il lève le nez. Ça sent la soupe. Une petite fumée danse. Tom ! Viens, Tom ! La soupe est prête. Tom arrive. Il voit sa chaise. La chaise est un peu loin. C'est mon bateau ! Oui. Ta chaise, c'est ton bateau. Tom s'assoit. Il pousse un peu. Le bateau va jusqu'à la table. Papa s'assoit aussi. Maman s'assoit près de Tom.</t>
+          <t>Tom est dans le couloir. Il lève le nez. Ça sent la soupe. Une petite fumée danse. Tom ! Viens, Tom ! La soupe est prête. Tom marche vers la cuisine. Il arrive. Il voit les assiettes. Il voit sa chaise. La chaise est un peu loin. C'est mon bateau ! Oui. Ta chaise, c'est ton bateau. Tom s'assoit. Il pose les mains sur la chaise. Il pousse un peu. Le bateau glisse. Le bateau va jusqu'à la table. Papa s'assoit aussi. Maman s'assoit près de Tom. On est ensemble. On est à table. Tom est bien assis. Ses pieds touchent la barre. Il pose les mains sur la table. Il regarde papa. Il regarde maman. La soupe fume tout près. Tom regarde la fumée. La fumée danse encore. Tom attend. Le bateau ne bouge plus. Tom respire. Ça sent encore la soupe. Il est bien, à table. Papa est là. Maman est là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1331,17 +1336,38 @@
 papa|Tom !
 papa|Viens, Tom !
 maman|La soupe est prête.
-narrateur|Tom arrive.
+narrateur|Tom marche vers la cuisine.
+narrateur|Il arrive.
+narrateur|Il voit les assiettes.
 narrateur|Il voit sa chaise.
 narrateur|La chaise est un peu loin.
 enfant-m|C'est mon bateau !
 papa|Oui.
 papa|Ta chaise, c'est ton bateau.
 narrateur|Tom s'assoit.
+narrateur|Il pose les mains sur la chaise.
 narrateur|Il pousse un peu.
+narrateur|Le bateau glisse.
 narrateur|Le bateau va jusqu'à la table.
 narrateur|Papa s'assoit aussi.
-narrateur|Maman s'assoit près de Tom.</t>
+narrateur|Maman s'assoit près de Tom.
+maman|On est ensemble.
+maman|On est à table.
+narrateur|Tom est bien assis.
+narrateur|Ses pieds touchent la barre.
+narrateur|Il pose les mains sur la table.
+narrateur|Il regarde papa.
+narrateur|Il regarde maman.
+narrateur|La soupe fume tout près.
+narrateur|Tom regarde la fumée.
+narrateur|La fumée danse encore.
+narrateur|Tom attend.
+narrateur|Le bateau ne bouge plus.
+narrateur|Tom respire.
+narrateur|Ça sent encore la soupe.
+narrateur|Il est bien, à table.
+narrateur|Papa est là.
+narrateur|Maman est là.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1558,7 +1584,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom est assis. Il est à table. Papa et maman sont avec lui. On est ensemble.</t>
+          <t>Tom est assis. Il est à table. Papa est assis. Maman est assise. Ils sont ensemble. La soupe attend. Tom reste sur son bateau. Il attend un petit moment.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1704,8 +1730,12 @@
         <is>
           <t>narrateur|Tom est assis.
 narrateur|Il est à table.
-narrateur|Papa et maman sont avec lui.
-maman|On est ensemble.</t>
+narrateur|Papa est assis.
+narrateur|Maman est assise.
+maman|Ils sont ensemble.
+narrateur|La soupe attend.
+narrateur|Tom reste sur son bateau.
+narrateur|Il attend un petit moment.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1733,7 +1763,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La soupe est là. Tom prend sa cuillère. C'est chaud. C'est bon. Bon appétit, Tom. Ils mangent ensemble. Tom reste assis. Merci, maman. Merci, papa.</t>
+          <t>La soupe est là. Tom prend sa cuillère. Il attend un peu. Il goûte. C'est chaud. C'est bon. Une petite cuillère. Bon appétit, Tom. Ils mangent ensemble. Tom reste assis. Encore une cuillère. Le bateau ne part pas. Tom est encore assis. Papa mange aussi. Maman mange aussi. Merci, maman. Merci, papa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1875,11 +1905,19 @@
         <is>
           <t>narrateur|La soupe est là.
 narrateur|Tom prend sa cuillère.
+narrateur|Il attend un peu.
+narrateur|Il goûte.
 enfant-m|C'est chaud.
 enfant-m|C'est bon.
+narrateur|Une petite cuillère.
 maman|Bon appétit, Tom.
 narrateur|Ils mangent ensemble.
 narrateur|Tom reste assis.
+narrateur|Encore une cuillère.
+narrateur|Le bateau ne part pas.
+narrateur|Tom est encore assis.
+narrateur|Papa mange aussi.
+narrateur|Maman mange aussi.
 enfant-m|Merci, maman.
 enfant-m|Merci, papa.</t>
         </is>
@@ -1909,7 +1947,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La fumée s'en va. Le bateau de Tom reste à table. On a mangé assis, ensemble. L'histoire est finie.</t>
+          <t>La fumée s'en va. Le bateau de Tom reste à table. On a mangé assis, ensemble. C'était bon. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2052,6 +2090,7 @@
           <t>narrateur|La fumée s'en va.
 narrateur|Le bateau de Tom reste à table.
 maman|On a mangé assis, ensemble.
+enfant-m|C'était bon.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2074,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2124,6 +2163,34 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit captivant, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit captivant, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit captivant, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit captivant, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-008 récit captivant, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom est dans le couloir. Il lève le nez. Ça sent la soupe. Une petite fumée danse. Tom ! Viens, Tom ! La soupe est prête. Tom marche vers la cuisine. Il arrive. Il voit les assiettes. Il voit sa chaise. La chaise est un peu loin. C'est mon bateau ! Oui. Ta chaise, c'est ton bateau. Tom s'assoit. Il pose les mains sur la chaise. Il pousse un peu. Le bateau glisse. Le bateau va jusqu'à la table. Papa s'assoit aussi. Maman s'assoit près de Tom. On est ensemble. On est à table. Tom est bien assis. Ses pieds touchent la barre. Il pose les mains sur la table. Il regarde papa. Il regarde maman. La soupe fume tout près. Tom regarde la fumée. La fumée danse encore. Tom attend. Le bateau ne bouge plus. Tom respire. Ça sent encore la soupe. Il est bien, à table. Papa est là. Maman est là.</t>
+          <t>Tom est dans le couloir. Il lève le nez. Ça sent la soupe. Une petite fumée danse. Tom ! Viens, Tom ! La soupe est prête. Tom marche vers la cuisine. Il arrive. Il voit les assiettes. Il voit sa chaise. La chaise est un peu loin. C'est mon bateau ! Oui. Ta chaise, c'est ton bateau. Tu amènes ton bateau à table ? Tom s'assoit. Il pose les mains sur la chaise. Il pousse un peu. Le bateau glisse. Le bateau va jusqu'à la table. Bravo, Tom. Ton bateau est à table. Papa s'assoit aussi. Maman s'assoit près de Tom. On est ensemble. On est à table. Tu es bien assis. Bravo. Ses pieds touchent la barre. Tes pieds sont sur la barre ? Oui, maman. Tu poses les mains sur la table ? Il pose les mains sur la table. La soupe fume tout près. Tom regarde la fumée. Tu as vu la petite fumée ? Elle danse. On attend un petit moment. Le bateau ne bouge plus. Tom respire. Ça sent bon, hein ? Ça sent la soupe.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1344,30 +1344,33 @@
 enfant-m|C'est mon bateau !
 papa|Oui.
 papa|Ta chaise, c'est ton bateau.
+papa|Tu amènes ton bateau à table ?
 narrateur|Tom s'assoit.
 narrateur|Il pose les mains sur la chaise.
 narrateur|Il pousse un peu.
 narrateur|Le bateau glisse.
 narrateur|Le bateau va jusqu'à la table.
+papa|Bravo, Tom.
+papa|Ton bateau est à table.
 narrateur|Papa s'assoit aussi.
 narrateur|Maman s'assoit près de Tom.
 maman|On est ensemble.
 maman|On est à table.
-narrateur|Tom est bien assis.
+maman|Tu es bien assis. Bravo.
 narrateur|Ses pieds touchent la barre.
+maman|Tes pieds sont sur la barre ?
+enfant-m|Oui, maman.
+papa|Tu poses les mains sur la table ?
 narrateur|Il pose les mains sur la table.
-narrateur|Il regarde papa.
-narrateur|Il regarde maman.
 narrateur|La soupe fume tout près.
 narrateur|Tom regarde la fumée.
-narrateur|La fumée danse encore.
-narrateur|Tom attend.
+maman|Tu as vu la petite fumée ?
+enfant-m|Elle danse.
+papa|On attend un petit moment.
 narrateur|Le bateau ne bouge plus.
 narrateur|Tom respire.
-narrateur|Ça sent encore la soupe.
-narrateur|Il est bien, à table.
-narrateur|Papa est là.
-narrateur|Maman est là.</t>
+maman|Ça sent bon, hein ?
+enfant-m|Ça sent la soupe.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1584,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom est assis. Il est à table. Papa est assis. Maman est assise. Ils sont ensemble. La soupe attend. Tom reste sur son bateau. Il attend un petit moment.</t>
+          <t>Tom est assis. Il est à table. On est tous assis. On est ensemble. La soupe attend. Ton bateau reste à table ? Oui. Tom reste sur son bateau. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1730,12 +1733,13 @@
         <is>
           <t>narrateur|Tom est assis.
 narrateur|Il est à table.
-narrateur|Papa est assis.
-narrateur|Maman est assise.
-maman|Ils sont ensemble.
+papa|On est tous assis.
+maman|On est ensemble.
 narrateur|La soupe attend.
+papa|Ton bateau reste à table ?
+enfant-m|Oui.
 narrateur|Tom reste sur son bateau.
-narrateur|Il attend un petit moment.</t>
+maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1763,7 +1767,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La soupe est là. Tom prend sa cuillère. Il attend un peu. Il goûte. C'est chaud. C'est bon. Une petite cuillère. Bon appétit, Tom. Ils mangent ensemble. Tom reste assis. Encore une cuillère. Le bateau ne part pas. Tom est encore assis. Papa mange aussi. Maman mange aussi. Merci, maman. Merci, papa.</t>
+          <t>La soupe est là. Tu prends ta cuillère ? Tom prend sa cuillère. Tu attends un peu. C'est chaud. Il attend un peu. Il goûte. C'est chaud. C'est bon. Bravo, Tom. Tu as goûté. C'est du bon travail. Bon appétit. Bon appétit, Tom. Ils mangent ensemble. Tom reste assis. Encore une petite cuillère ? Encore une cuillère. Le bateau ne part pas. Tu restes assis. Bravo. Merci, maman. Merci, papa. Merci, Tom.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1904,22 +1908,27 @@
       <c r="AW5" t="inlineStr">
         <is>
           <t>narrateur|La soupe est là.
+maman|Tu prends ta cuillère ?
 narrateur|Tom prend sa cuillère.
+papa|Tu attends un peu. C'est chaud.
 narrateur|Il attend un peu.
 narrateur|Il goûte.
 enfant-m|C'est chaud.
 enfant-m|C'est bon.
-narrateur|Une petite cuillère.
-maman|Bon appétit, Tom.
+maman|Bravo, Tom.
+maman|Tu as goûté.
+maman|C'est du bon travail.
+maman|Bon appétit.
+papa|Bon appétit, Tom.
 narrateur|Ils mangent ensemble.
 narrateur|Tom reste assis.
+papa|Encore une petite cuillère ?
 narrateur|Encore une cuillère.
 narrateur|Le bateau ne part pas.
-narrateur|Tom est encore assis.
-narrateur|Papa mange aussi.
-narrateur|Maman mange aussi.
+papa|Tu restes assis. Bravo.
 enfant-m|Merci, maman.
-enfant-m|Merci, papa.</t>
+enfant-m|Merci, papa.
+maman|Merci, Tom.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1947,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La fumée s'en va. Le bateau de Tom reste à table. On a mangé assis, ensemble. C'était bon. L'histoire est finie.</t>
+          <t>La fumée s'en va. Le bateau de Tom reste à table. On a mangé assis, ensemble. C'était bon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2089,8 +2098,10 @@
         <is>
           <t>narrateur|La fumée s'en va.
 narrateur|Le bateau de Tom reste à table.
-maman|On a mangé assis, ensemble.
+papa|On a mangé assis, ensemble.
 enfant-m|C'était bon.
+maman|Bravo.
+maman|Tu as fait du bon travail.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2113,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2191,6 +2202,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit captivant, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit captivant, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le bateau de Tom</t>
+          <t>Le bateau de Nino</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>La chaise de Tom, c'est son bateau. Le bateau va jusqu'à la table. Tom s'assoit avec papa et maman. Il goûte la soupe. On mange.</t>
+          <t>Dehors il pleut. Dans la maison, ça sent la soupe. La chaise de Nino est son bateau. Le bateau va jusqu'à la table. On mange assis.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tom est dans le couloir. Il lève le nez. Ça sent la soupe. Une petite fumée danse. Tom ! Viens, Tom ! La soupe est prête. Tom marche vers la cuisine. Il arrive. Il voit les assiettes. Il voit sa chaise. La chaise est un peu loin. C'est mon bateau ! Oui. Ta chaise, c'est ton bateau. Tu amènes ton bateau à table ? Tom s'assoit. Il pose les mains sur la chaise. Il pousse un peu. Le bateau glisse. Le bateau va jusqu'à la table. Bravo, Tom. Ton bateau est à table. Papa s'assoit aussi. Maman s'assoit près de Tom. On est ensemble. On est à table. Tu es bien assis. Bravo. Ses pieds touchent la barre. Tes pieds sont sur la barre ? Oui, maman. Tu poses les mains sur la table ? Il pose les mains sur la table. La soupe fume tout près. Tom regarde la fumée. Tu as vu la petite fumée ? Elle danse. On attend un petit moment. Le bateau ne bouge plus. Tom respire. Ça sent bon, hein ? Ça sent la soupe.</t>
+          <t>Il pleut sur le village. Les gouttes tapent la gouttière. Tic. Tic. Tic. Nino ne va pas au parc, aujourd'hui. Le parc est trop mouillé. Dans la maison, c'est doux. Ça sent la soupe. Une petite fumée danse. Nino est dans le couloir. Il lève le nez. Nino ! Viens, Nino ! La soupe est prête. Nino marche vers la cuisine. Le carrelage est un peu froid. Il voit les assiettes. Il voit sa chaise. La chaise est un peu loin. C'est mon bateau ! Oui. Ta chaise, c'est ton bateau. Tu amènes ton bateau à table ? Nino s'assoit. Il pousse un peu. Le bateau glisse. Le bateau va jusqu'à la table. Bravo, Nino. Ton bateau est à table. Papa s'assoit aussi. Maman s'assoit près de Nino. On est ensemble. On est à table. Tu es bien assis. Bravo. Ses pieds touchent la barre. Tes pieds sont sur la barre ? Oui, maman. Tu poses les mains sur la table ? Il pose les mains sur la table. La soupe fume tout près. Tu as vu la petite fumée ? Elle danse. On attend un petit moment. Le bateau ne bouge plus. Ça sent bon, hein ? Ça sent la soupe.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1329,15 +1329,21 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Tom est dans le couloir.
-narrateur|Il lève le nez.
+          <t>narrateur|Il pleut sur le village.
+narrateur|Les gouttes tapent la gouttière.
+narrateur|Tic. Tic. Tic.
+narrateur|Nino ne va pas au parc, aujourd'hui.
+narrateur|Le parc est trop mouillé.
+narrateur|Dans la maison, c'est doux.
 narrateur|Ça sent la soupe.
 narrateur|Une petite fumée danse.
-papa|Tom !
-papa|Viens, Tom !
+narrateur|Nino est dans le couloir.
+narrateur|Il lève le nez.
+papa|Nino !
+papa|Viens, Nino !
 maman|La soupe est prête.
-narrateur|Tom marche vers la cuisine.
-narrateur|Il arrive.
+narrateur|Nino marche vers la cuisine.
+narrateur|Le carrelage est un peu froid.
 narrateur|Il voit les assiettes.
 narrateur|Il voit sa chaise.
 narrateur|La chaise est un peu loin.
@@ -1345,15 +1351,14 @@
 papa|Oui.
 papa|Ta chaise, c'est ton bateau.
 papa|Tu amènes ton bateau à table ?
-narrateur|Tom s'assoit.
-narrateur|Il pose les mains sur la chaise.
+narrateur|Nino s'assoit.
 narrateur|Il pousse un peu.
 narrateur|Le bateau glisse.
 narrateur|Le bateau va jusqu'à la table.
-papa|Bravo, Tom.
+papa|Bravo, Nino.
 papa|Ton bateau est à table.
 narrateur|Papa s'assoit aussi.
-narrateur|Maman s'assoit près de Tom.
+narrateur|Maman s'assoit près de Nino.
 maman|On est ensemble.
 maman|On est à table.
 maman|Tu es bien assis. Bravo.
@@ -1363,12 +1368,10 @@
 papa|Tu poses les mains sur la table ?
 narrateur|Il pose les mains sur la table.
 narrateur|La soupe fume tout près.
-narrateur|Tom regarde la fumée.
 maman|Tu as vu la petite fumée ?
 enfant-m|Elle danse.
 papa|On attend un petit moment.
 narrateur|Le bateau ne bouge plus.
-narrateur|Tom respire.
 maman|Ça sent bon, hein ?
 enfant-m|Ça sent la soupe.</t>
         </is>
@@ -1402,7 +1405,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le bateau s'arrête. Tom est où ?</t>
+          <t>Le bateau s'arrête. Nino est où ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1559,7 +1562,7 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Le bateau s'arrête.
-narrateur|Tom est où ?</t>
+narrateur|Nino est où ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1587,7 +1590,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom est assis. Il est à table. On est tous assis. On est ensemble. La soupe attend. Ton bateau reste à table ? Oui. Tom reste sur son bateau. Bravo. Tu attends un petit moment.</t>
+          <t>Nino est assis. Il est à table. On est tous assis. On est ensemble. La soupe attend. Ton bateau reste à table ? Oui. Nino reste sur son bateau. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1731,14 +1734,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Tom est assis.
+          <t>narrateur|Nino est assis.
 narrateur|Il est à table.
 papa|On est tous assis.
 maman|On est ensemble.
 narrateur|La soupe attend.
 papa|Ton bateau reste à table ?
 enfant-m|Oui.
-narrateur|Tom reste sur son bateau.
+narrateur|Nino reste sur son bateau.
 maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
@@ -1767,7 +1770,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La soupe est là. Tu prends ta cuillère ? Tom prend sa cuillère. Tu attends un peu. C'est chaud. Il attend un peu. Il goûte. C'est chaud. C'est bon. Bravo, Tom. Tu as goûté. C'est du bon travail. Bon appétit. Bon appétit, Tom. Ils mangent ensemble. Tom reste assis. Encore une petite cuillère ? Encore une cuillère. Le bateau ne part pas. Tu restes assis. Bravo. Merci, maman. Merci, papa. Merci, Tom.</t>
+          <t>La soupe est là. Tu prends ta cuillère ? Nino prend sa cuillère. Tu attends un peu. C'est chaud. Il attend un peu. Il goûte. C'est chaud. C'est bon. Bravo, Nino. Tu as goûté. C'est du bon travail. Bon appétit. Bon appétit, Nino. Ils mangent ensemble. Nino reste assis. Encore une petite cuillère ? Encore une cuillère. Le bateau ne part pas. Tu restes assis. Bravo. Merci, maman. Merci, papa. Merci, Nino.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1909,26 +1912,26 @@
         <is>
           <t>narrateur|La soupe est là.
 maman|Tu prends ta cuillère ?
-narrateur|Tom prend sa cuillère.
+narrateur|Nino prend sa cuillère.
 papa|Tu attends un peu. C'est chaud.
 narrateur|Il attend un peu.
 narrateur|Il goûte.
 enfant-m|C'est chaud.
 enfant-m|C'est bon.
-maman|Bravo, Tom.
+maman|Bravo, Nino.
 maman|Tu as goûté.
 maman|C'est du bon travail.
 maman|Bon appétit.
-papa|Bon appétit, Tom.
+papa|Bon appétit, Nino.
 narrateur|Ils mangent ensemble.
-narrateur|Tom reste assis.
+narrateur|Nino reste assis.
 papa|Encore une petite cuillère ?
 narrateur|Encore une cuillère.
 narrateur|Le bateau ne part pas.
 papa|Tu restes assis. Bravo.
 enfant-m|Merci, maman.
 enfant-m|Merci, papa.
-maman|Merci, Tom.</t>
+maman|Merci, Nino.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1956,7 +1959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La fumée s'en va. Le bateau de Tom reste à table. On a mangé assis, ensemble. C'était bon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>La fumée s'en va. Le bateau de Nino reste à table. On a mangé assis, ensemble. C'était bon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2097,7 +2100,7 @@
       <c r="AW6" t="inlineStr">
         <is>
           <t>narrateur|La fumée s'en va.
-narrateur|Le bateau de Tom reste à table.
+narrateur|Le bateau de Nino reste à table.
 papa|On a mangé assis, ensemble.
 enfant-m|C'était bon.
 maman|Bravo.
@@ -2124,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2211,6 +2214,13 @@
       <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit captivant, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;C'est l'heure du dîner. Tom est dans la cuisine. Papa pose les assiettes. Maman apporte le pain. Tom va s'asseoir. Il pose les fesses sur la chaise. Il est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt; à table. Papa s'assoit aussi. Maman s'assoit près de Tom. Ils mangent ensemble. Tom tient sa cuillère. Il mange assis. La chaise est stable. Papa dit : on mange ensemble, à table. Tom sourit. Il reste assis. Maman coupe le pain. Tom attend, assis. Ils sont ensemble à table.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Il pleut sur le village. Les gouttes tapent la gouttière. Tic. Tic. Tic. Nino ne va pas au parc, aujourd'hui. Le parc est trop mouillé. Dans la maison, c'est doux. Ça sent la soupe. Une petite fumée danse. Nino est dans le couloir. Il lève le nez. Nino ! Viens, Nino ! La soupe est prête. Nino marche vers la cuisine. Le carrelage est un peu froid. Il voit les assiettes. Il voit sa chaise. La chaise est un peu loin. C'est mon bateau ! Oui. Ta chaise, c'est ton bateau. Tu amènes ton bateau à table ? Nino s'assoit. Il pousse un peu. Le bateau glisse. Le bateau va jusqu'à la table. Bravo, Nino. Ton bateau est à table. Papa s'assoit aussi. Maman s'assoit près de Nino. On est ensemble. On est à table. Tu es bien assis. Bravo. Ses pieds touchent la barre. Tes pieds sont sur la barre ? Oui, maman. Tu poses les mains sur la table ? Il pose les mains sur la table. La soupe fume tout près. Tu as vu la petite fumée ? Elle danse. On attend un petit moment. Le bateau ne bouge plus. Ça sent bon, hein ? Ça sent la soupe.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Tom va manger. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le bateau s'arrête. Nino est où ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1565,7 +1565,6 @@
 narrateur|Nino est où ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1595,7 +1594,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Tom est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino est assis. Il est à table. On est tous assis. On est ensemble. La soupe attend. Ton bateau reste à table ? Oui. Nino reste sur son bateau. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1745,7 +1744,6 @@
 maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1770,12 +1768,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La soupe est là. Tu prends ta cuillère ? Nino prend sa cuillère. Tu attends un peu. C'est chaud. Il attend un peu. Il goûte. C'est chaud. C'est bon. Bravo, Nino. Tu as goûté. C'est du bon travail. Bon appétit. Bon appétit, Nino. Ils mangent ensemble. Nino reste assis. Encore une petite cuillère ? Encore une cuillère. Le bateau ne part pas. Tu restes assis. Bravo. Merci, maman. Merci, papa. Merci, Nino.</t>
+          <t>La soupe est là. Tu prends ta cuillère ? Nino prend sa cuillère. Tu attends un peu. C'est chaud. Il attend un peu. Il goûte. C'est chaud. C'est bon. Bravo, Nino. Tu as goûté. Bon appétit. Bon appétit, Nino. Ils mangent ensemble. Nino reste assis. Encore une petite cuillère ? Encore une cuillère. Le bateau ne part pas. Tu restes assis. Bravo. Merci, maman. Merci, papa. Merci, Nino.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Tom boit une gorgée. Il reste &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt; jusqu'à la fin. Merci, dit maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La soupe est là. Tu prends ta cuillère ? Nino prend sa cuillère. Tu attends un peu. C'est chaud. Il attend un peu. Il goûte. C'est chaud. C'est bon. Bravo, Nino. Tu as goûté. Bon appétit. Bon appétit, Nino. Ils mangent ensemble. Nino reste assis. Encore une petite cuillère ? Encore une cuillère. Le bateau ne part pas. Tu restes assis. Bravo. Merci, maman. Merci, papa. Merci, Nino.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1920,7 +1918,6 @@
 enfant-m|C'est bon.
 maman|Bravo, Nino.
 maman|Tu as goûté.
-maman|C'est du bon travail.
 maman|Bon appétit.
 papa|Bon appétit, Nino.
 narrateur|Ils mangent ensemble.
@@ -1934,7 +1931,6 @@
 maman|Merci, Nino.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1959,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La fumée s'en va. Le bateau de Nino reste à table. On a mangé assis, ensemble. C'était bon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>La fumée s'en va. Le bateau de Nino reste à table. On a mangé assis, ensemble. C'était bon. Bravo.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La fumée s'en va. Le bateau de Nino reste à table. On a mangé assis, ensemble. C'était bon. Bravo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,12 +2099,9 @@
 narrateur|Le bateau de Nino reste à table.
 papa|On a mangé assis, ensemble.
 enfant-m|C'était bon.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2221,6 +2214,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-01.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tom, papa, maman</t>
+          <t>Nino, papa, maman</t>
         </is>
       </c>
     </row>
